--- a/sharedata/excel/S-属性表(AttributeData).xlsx
+++ b/sharedata/excel/S-属性表(AttributeData).xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\策划文档\配置表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ThroneOfAshes_Client\sharedata\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="属性表(AttributeData)" sheetId="4" r:id="rId1"/>
@@ -208,13 +208,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
@@ -849,16 +849,16 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1336,239 +1336,239 @@
   <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="18.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.25" style="1" customWidth="1"/>
-    <col min="5" max="8" width="19.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="24.375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="19.125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="21.25" style="3" customWidth="1"/>
+    <col min="5" max="8" width="19.125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1"/>
     <row r="2" customHeight="1"/>
-    <row r="3" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:8">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A4" s="3" t="s">
+    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:8">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A5" s="3" t="s">
+    <row r="5" s="2" customFormat="1" customHeight="1" spans="1:8">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A6" s="3" t="s">
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:8">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1" t="s">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1" t="s">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1" t="s">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1" t="s">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1" t="s">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D11" s="4"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1" t="s">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D12" s="4"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1" t="s">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1" t="s">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
     </row>
     <row r="15" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1" t="s">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1" t="s">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1" t="s">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
     </row>
     <row r="18" customHeight="1" spans="1:8">
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="3" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1584,149 +1584,148 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="21.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.125" style="1" customWidth="1"/>
-    <col min="6" max="9" width="19.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="21.375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="19.125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="18.5" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.125" style="3" customWidth="1"/>
+    <col min="6" max="9" width="19.125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1"/>
     <row r="2" customHeight="1"/>
-    <row r="3" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="4" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A4" s="3" t="s">
+    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="5" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A5" s="3" t="s">
+    <row r="5" s="2" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A6" s="3" t="s">
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="3"/>
     </row>
     <row r="7" customHeight="1" spans="1:5">
-      <c r="B7" s="1">
+      <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:5">
-      <c r="B8" s="1">
+      <c r="B8" s="3">
         <v>2</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:5">
-      <c r="B9" s="1">
+      <c r="B9" s="3">
         <v>3</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:5">
-      <c r="B10" s="1">
+      <c r="B10" s="3">
         <v>4</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:5">
-      <c r="B11" s="1">
+      <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="3" t="s">
         <v>47</v>
       </c>
     </row>
